--- a/app-configuracion-sociedades/checklist/Checklist_Configuracion_Sociedad_SAP.xlsx
+++ b/app-configuracion-sociedades/checklist/Checklist_Configuracion_Sociedad_SAP.xlsx
@@ -5,7 +5,9 @@
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
     <sheet name="Checklist Configuración" sheetId="2" r:id="rId2"/>
     <sheet name="Datos Maestros" sheetId="3" r:id="rId3"/>
-    <sheet name="Áreas y Responsabilidades" sheetId="4" r:id="rId4"/>
+    <sheet name="Detalle Datos Maestros" sheetId="4" r:id="rId4"/>
+    <sheet name="Arranque 1er Asiento" sheetId="5" r:id="rId5"/>
+    <sheet name="Áreas y Responsabilidades" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -107,7 +109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="120" customWidth="1"/>
+    <col min="1" max="1" width="130" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -127,7 +129,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generado automáticamente desde el catálogo de preguntas de la app low-code (54 preguntas, 14 módulos/secciones).</t>
+          <t xml:space="preserve">Generado automáticamente desde el catálogo de preguntas de la app low-code (57 preguntas, 14 módulos/secciones).</t>
         </is>
       </c>
     </row>
@@ -141,61 +143,75 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cómo usar este archivo:</t>
+          <t xml:space="preserve">Hojas de este libro:</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Hoja «Checklist Configuración»: una fila por cada definición requerida, con la actividad SAP, la transacción y el área responsable. Use la columna Estado (Pendiente / En proceso / Listo / N/A) para hacer seguimiento.</t>
+          <t xml:space="preserve">1. «Checklist Configuración»: una fila por cada definición del cuestionario, con actividad SAP, transacción y áreas responsables. Use la columna Estado (Pendiente / En proceso / Listo / N/A).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Hoja «Datos Maestros»: objetos de datos maestros a definir y cargar, con el área que define, crea y aprueba cada uno.</t>
+          <t xml:space="preserve">2. «Datos Maestros»: resumen de los objetos de datos maestros con quién define, crea/carga y aprueba cada uno.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Hoja «Áreas y Responsabilidades»: glosario de áreas de negocio y técnicas involucradas.</t>
+          <t xml:space="preserve">3. «Detalle Datos Maestros»: nivel de campo y decisión por objeto — CECOs, CEBEs, BPs (por rol), cuentas, activos, bancos y parametrizaciones operativas (tolerancias, clases de documento, tipos de cambio).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. «Arranque 1er Asiento»: secuencia ordenada de verificación con criterios de aceptación; todos los pasos bloqueantes deben estar en «Listo» antes de contabilizar el primer documento.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. «Áreas y Responsabilidades»: glosario de áreas de negocio y técnicas involucradas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Notas:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Las filas se generan a partir de las preguntas vigentes; si agrega o edita preguntas en la app, vuelva a generar el checklist con: node scripts/generar-checklist.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Los nombres de áreas son una propuesta estándar; ajústelos a la estructura organizacional de su compañía.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Las filas del checklist se generan desde las preguntas vigentes; si edita preguntas en la app, regenere con: node scripts/generar-checklist.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• Los nombres de áreas son una propuesta estándar; ajústelos a la estructura organizacional de su compañía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">• La parametrización debe ejecutarse y validarse en SAP por personal funcional, siguiendo la estrategia de transportes del proyecto.</t>
         </is>
@@ -1533,344 +1549,344 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Impuestos y retenciones</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Contabilidad principal (GL)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se requiere reporting por segmentos (NIIF 8 / unidades de negocio en estados financieros)?</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definir segmentos y su derivación desde centros de beneficio</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPRO</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAGL_SEGM / CEPC-SEGMENT</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-GL</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Segmentos para revelar resultados y posición financiera por línea de negocio.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2. Contabilidad principal (GL)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿El balance debe cuadrar a nivel de centro de beneficio y/o segmento (desglose de documentos)?</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activar y configurar el desglose de documentos (document splitting)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPRO (varias actividades)</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAGL_SPLINFO / clasificación de cuentas y clases de documento</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-GL</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Document splitting: cada partida del documento se enriquece con CeBe/segmento y el balance cierra por esas características.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">3. Impuestos y retenciones</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Impuestos y retenciones</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">¿La sociedad aplica retenciones en la fuente (withholding tax)?</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Configurar retención ampliada (extended withholding tax)</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SPRO (varias actividades)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">T059P / T059Z / T001-WT_NEWWT</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Área Tributaria / Impuestos</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Consultor FI (Tax)</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Retenciones de renta, IVA, ICA u otras según legislación local.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. Impuestos y retenciones</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Qué indicadores de IVA/impuestos necesita la sociedad?</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elegir una opción: Copiar indicadores estándar del país | Crear indicadores específicos (tarifas locales propias)</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verificar/copiar indicadores de IVA estándar; Crear indicadores de IVA con tarifas locales</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FTXP, OB40</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T007A / T007S, T007A / T030K</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Área Tributaria / Impuestos</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor FI (Tax)</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Indicadores de impuesto soportado y repercutido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. Cuentas por pagar (AP)</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3. Impuestos y retenciones</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Qué indicadores de IVA/impuestos necesita la sociedad?</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elegir una opción: Copiar indicadores estándar del país | Crear indicadores específicos (tarifas locales propias)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verificar/copiar indicadores de IVA estándar; Crear indicadores de IVA con tarifas locales</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTXP, OB40</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T007A / T007S, T007A / T030K</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área Tributaria / Impuestos</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI (Tax)</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indicadores de impuesto soportado y repercutido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">4. Cuentas por pagar (AP)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿La sociedad gestionará cuentas por pagar (proveedores)?</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preparar AP: grupos de cuentas de proveedor y cuentas asociadas</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BP, OBD3, FS00</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T077K / LFB1-AKONT</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cuentas por Pagar</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor FI-AP</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Compras a crédito, facturas de proveedores y pagos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. Cuentas por pagar (AP)</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Se usará el programa de pagos automáticos?</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Configurar programa de pagos automáticos; Pagos manuales</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FBZP (config.), F110 (ejecución), F-53, F-58</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T042 (todas las subtablas)</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cuentas por Pagar</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor FI-AP</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generación masiva de pagos (transferencias, cheques) con propuesta y ejecución.</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -1887,7 +1903,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Se pagarán anticipos a proveedores?</t>
+          <t xml:space="preserve">¿La sociedad gestionará cuentas por pagar (proveedores)?</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1897,17 +1913,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configurar operaciones CME de anticipos a acreedores</t>
+          <t xml:space="preserve">Preparar AP: grupos de cuentas de proveedor y cuentas asociadas</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBYR</t>
+          <t xml:space="preserve">BP, OBD3, FS00</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T074</t>
+          <t xml:space="preserve">T077K / LFB1-AKONT</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1927,178 +1943,178 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pagos antes de recibir la factura (operaciones en cuenta de mayor especial).</t>
+          <t xml:space="preserve">Compras a crédito, facturas de proveedores y pagos.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5. Cuentas por cobrar y crédito (AR)</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Cuentas por pagar (AP)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se usará el programa de pagos automáticos?</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configurar programa de pagos automáticos; Pagos manuales</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FBZP (config.), F110 (ejecución), F-53, F-58</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T042 (todas las subtablas)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas por Pagar</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AP</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generación masiva de pagos (transferencias, cheques) con propuesta y ejecución.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">4. Cuentas por pagar (AP)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se pagarán anticipos a proveedores?</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configurar operaciones CME de anticipos a acreedores</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBYR</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T074</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas por Pagar</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AP</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pagos antes de recibir la factura (operaciones en cuenta de mayor especial).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">5. Cuentas por cobrar y crédito (AR)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿La sociedad gestionará cuentas por cobrar (clientes)?</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preparar AR: grupos de cuentas de cliente y cuentas asociadas</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BP, OBD2, FS00</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T077D / KNB1-AKONT</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cartera / Crédito y Cobranza</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor FI-AR</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ventas a crédito, facturas de clientes y cobranza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5. Cuentas por cobrar y crédito (AR)</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Se recibirán anticipos de clientes?</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Configurar operaciones CME de anticipos de deudores</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OBXR</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T074</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cartera / Crédito y Cobranza</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor FI-AR</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cobros antes de emitir la factura (operaciones en cuenta de mayor especial).</t>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2115,7 +2131,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Se enviarán recordatorios o reclamaciones de cobro a clientes (dunning)?</t>
+          <t xml:space="preserve">¿La sociedad gestionará cuentas por cobrar (clientes)?</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2125,17 +2141,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definir procedimiento de reclamación</t>
+          <t xml:space="preserve">Preparar AR: grupos de cuentas de cliente y cuentas asociadas</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FBMP (config.), F150 (ejecución)</t>
+          <t xml:space="preserve">BP, OBD2, FS00</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T047 (todas las subtablas)</t>
+          <t xml:space="preserve">T077D / KNB1-AKONT</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2155,7 +2171,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartas/correos automáticos por niveles de mora.</t>
+          <t xml:space="preserve">Ventas a crédito, facturas de clientes y cobranza.</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2188,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿La sociedad requiere gestión de crédito de clientes?</t>
+          <t xml:space="preserve">¿Se recibirán anticipos de clientes?</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2182,17 +2198,17 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configurar gestión de crédito (FSCM Credit Management)</t>
+          <t xml:space="preserve">Configurar operaciones CME de anticipos de deudores</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UKM_MY_DCDS, BP, OB38</t>
+          <t xml:space="preserve">OBXR</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T001-KKBER / UKMBP_CMS_SGM</t>
+          <t xml:space="preserve">T074</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2212,178 +2228,178 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control de límites de crédito para clientes en ventas.</t>
+          <t xml:space="preserve">Cobros antes de emitir la factura (operaciones en cuenta de mayor especial).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6. Activos fijos (AA)</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. Cuentas por cobrar y crédito (AR)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se enviarán recordatorios o reclamaciones de cobro a clientes (dunning)?</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definir procedimiento de reclamación</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FBMP (config.), F150 (ejecución)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T047 (todas las subtablas)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartera / Crédito y Cobranza</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AR</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartas/correos automáticos por niveles de mora.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">31</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5. Cuentas por cobrar y crédito (AR)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿La sociedad requiere gestión de crédito de clientes?</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configurar gestión de crédito (FSCM Credit Management)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UKM_MY_DCDS, BP, OB38</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T001-KKBER / UKMBP_CMS_SGM</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartera / Crédito y Cobranza</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AR</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control de límites de crédito para clientes en ventas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">6. Activos fijos (AA)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿La sociedad gestionará activos fijos?</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Activar contabilidad de activos fijos para la sociedad</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OAOB</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T093C</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contabilidad de Activos Fijos</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor FI-AA</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Propiedad, planta y equipo; intangibles; activos en curso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6. Activos fijos (AA)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Se tendrá el mismo plan de valoración de alguna otra sociedad existente o uno nuevo?</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elegir una opción: Mismo plan de valoración de otra sociedad | Plan de valoración nuevo (copiado de referencia)</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asignar plan de valoración existente a la sociedad; Copiar plan de valoración de referencia y ajustarlo</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OAOB, EC08, OADB</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T093C-AFAPL, T093 / T093A</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contabilidad de Activos Fijos</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor FI-AA</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El plan de valoración define las áreas de valoración (local, NIIF, fiscal).</t>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2400,27 +2416,27 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Qué clases de activos fijos se tendrán?</t>
+          <t xml:space="preserve">¿La sociedad gestionará activos fijos?</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seleccionar valor(es) del catálogo «Clases de activos fijos».</t>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definir clases de activos y determinación de cuentas</t>
+          <t xml:space="preserve">Activar contabilidad de activos fijos para la sociedad</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OAOA, AO90</t>
+          <t xml:space="preserve">OAOB</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANKA / T095</t>
+          <t xml:space="preserve">T093C</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2440,7 +2456,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agregue todas las clases que apliquen; puede ampliar el catálogo con las clases propias de su compañía.</t>
+          <t xml:space="preserve">Propiedad, planta y equipo; intangibles; activos en curso.</t>
         </is>
       </c>
     </row>
@@ -2457,27 +2473,27 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Las vidas útiles y métodos de amortización siguen la política corporativa o la normativa local?</t>
+          <t xml:space="preserve">¿Se tendrá el mismo plan de valoración de alguna otra sociedad existente o uno nuevo?</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elegir una opción: Política corporativa existente | Normativa local (claves propias)</t>
+          <t xml:space="preserve">Elegir una opción: Mismo plan de valoración de otra sociedad | Plan de valoración nuevo (copiado de referencia)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Usar claves de amortización corporativas; Crear claves de amortización según normativa local</t>
+          <t xml:space="preserve">Asignar plan de valoración existente a la sociedad; Copiar plan de valoración de referencia y ajustarlo</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AFAMA</t>
+          <t xml:space="preserve">OAOB, EC08, OADB</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T090NAZ</t>
+          <t xml:space="preserve">T093C-AFAPL, T093 / T093A</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2497,178 +2513,178 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claves de amortización por área de valoración.</t>
+          <t xml:space="preserve">El plan de valoración define las áreas de valoración (local, NIIF, fiscal).</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7. Controlling (CO)</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Activos fijos (AA)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Qué clases de activos fijos se tendrán?</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seleccionar valor(es) del catálogo «Clases de activos fijos».</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definir clases de activos y determinación de cuentas</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OAOA, AO90</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANKA / T095</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad de Activos Fijos</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AA</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agregue todas las clases que apliquen; puede ampliar el catálogo con las clases propias de su compañía.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">6. Activos fijos (AA)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Las vidas útiles y métodos de amortización siguen la política corporativa o la normativa local?</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elegir una opción: Política corporativa existente | Normativa local (claves propias)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usar claves de amortización corporativas; Crear claves de amortización según normativa local</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AFAMA</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T090NAZ</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad de Activos Fijos</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AA</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claves de amortización por área de valoración.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">7. Controlling (CO)</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿La sociedad utilizará Controlling (contabilidad de costos)?</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Activar componentes de Controlling para la sociedad</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OKKP</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TKA00 / TKA01</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Costos / Planeación</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor CO</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Centros de coste, órdenes internas, análisis de rentabilidad, etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7. Controlling (CO)</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿La sociedad se asignará a una sociedad CO (área de controlling) existente o nueva?</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elegir una opción: Asignar a sociedad CO existente | Crear sociedad CO nueva</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Asignar sociedad a la sociedad CO existente; Crear sociedad CO y asignar la sociedad</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX19, OKKP</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TKA02, TKA01 / TKA02</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Costos / Planeación</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor CO</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Una sociedad CO puede agrupar varias sociedades FI (controlling entre sociedades).</t>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -2685,7 +2701,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Se requiere crear estructura de centros de coste para la nueva sociedad?</t>
+          <t xml:space="preserve">¿La sociedad utilizará Controlling (contabilidad de costos)?</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2695,17 +2711,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crear jerarquía estándar y centros de coste</t>
+          <t xml:space="preserve">Activar componentes de Controlling para la sociedad</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OKEON, KS01</t>
+          <t xml:space="preserve">OKKP</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CSKS / SETNODE</t>
+          <t xml:space="preserve">TKA00 / TKA01</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2725,7 +2741,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jerarquía estándar y centros de coste iniciales.</t>
+          <t xml:space="preserve">Centros de coste, órdenes internas, análisis de rentabilidad, etc.</t>
         </is>
       </c>
     </row>
@@ -2742,121 +2758,121 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Se usarán órdenes internas para control de gastos o proyectos menores?</t>
+          <t xml:space="preserve">¿La sociedad se asignará a una sociedad CO (área de controlling) existente o nueva?</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Elegir una opción: Asignar a sociedad CO existente | Crear sociedad CO nueva</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignar sociedad a la sociedad CO existente; Crear sociedad CO y asignar la sociedad</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OX19, OKKP</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TKA02, TKA01 / TKA02</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Una sociedad CO puede agrupar varias sociedades FI (controlling entre sociedades).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7. Controlling (CO)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se requiere crear estructura de centros de coste para la nueva sociedad?</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Definir tipos de órdenes internas y perfiles de liquidación</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KOT2_OPA, OKO7</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T003O</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crear jerarquía estándar y centros de coste</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OKEON, KS01</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSKS / SETNODE</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Costos / Planeación</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Consultor CO</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Colectores de costes temporales (campañas, eventos, reparaciones, CAPEX menor).</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Control presupuestal (FM)</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jerarquía estándar y centros de coste iniciales.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38</t>
+          <t xml:space="preserve">39</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8. Control presupuestal (FM)</t>
+          <t xml:space="preserve">7. Controlling (CO)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Habrá control presupuestal (Funds Management)?</t>
+          <t xml:space="preserve">¿Se usarán órdenes internas para control de gastos o proyectos menores?</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2866,27 +2882,27 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Activar gestión presupuestaria (FM-BCS) para la sociedad</t>
+          <t xml:space="preserve">Definir tipos de órdenes internas y perfiles de liquidación</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OF18, FMUF</t>
+          <t xml:space="preserve">KOT2_OPA, OKO7</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FM01 / T001-FIKRS</t>
+          <t xml:space="preserve">T003O</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presupuesto / Planeación Financiera</t>
+          <t xml:space="preserve">Costos / Planeación</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor FM</t>
+          <t xml:space="preserve">Consultor CO</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -2896,225 +2912,225 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control de ejecución del gasto contra presupuesto aprobado.</t>
+          <t xml:space="preserve">Colectores de costes temporales (campañas, eventos, reparaciones, CAPEX menor).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">7. Controlling (CO)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se gestionarán centros de beneficio (CEBE) para medir resultados por línea o unidad de negocio?</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definir jerarquía estándar y centros de beneficio (CEBE); Definir un centro de beneficio único por defecto</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KCH1 (jerarquía), KE51 (CeBe), 0KE5, KE51, FAGL3KEH</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEPC / SETNODE / TKA01-PHINR, CEPC</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Los CEBE permiten estados de resultados internos por unidad, línea de producto o región.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">8. Control presupuestal (FM)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Cómo se estructurará el presupuesto (centros gestores y posiciones presupuestarias)?</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proporcionar el dato solicitado.</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crear centros gestores y posiciones presupuestarias</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FMSA (centros gestores), FMCIA (posiciones)</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FMFCTR / FMCI</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Control presupuestal (FM)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Habrá control presupuestal (Funds Management)?</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activar gestión presupuestaria (FM-BCS) para la sociedad</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OF18, FMUF</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FM01 / T001-FIKRS</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Presupuesto / Planeación Financiera</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Consultor FM</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ej.: centros gestores por gerencia y posiciones por naturaleza del gasto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8. Control presupuestal (FM)</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Se necesitará control de imputación para ejecuciones de proyectos (CAPEX / OPEX)?</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Configurar derivación de imputaciones presupuestarias y control de disponibilidad</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FMDERIVE, OF39</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Estrategia de derivación FM / FMAVC</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Presupuesto / Planeación Financiera</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor FM</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Que el gasto de proyectos consuma presupuesto según su clasificación CAPEX u OPEX.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9. Proyectos (PS)</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control de ejecución del gasto contra presupuesto aprobado.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41</t>
+          <t xml:space="preserve">42</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9. Proyectos (PS)</t>
+          <t xml:space="preserve">8. Control presupuestal (FM)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿La sociedad ejecutará proyectos (inversión u obras) con el módulo PS?</t>
+          <t xml:space="preserve">¿Cómo se estructurará el presupuesto (centros gestores y posiciones presupuestarias)?</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+          <t xml:space="preserve">Proporcionar el dato solicitado.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definir perfil de proyecto y máscara de codificación PEP</t>
+          <t xml:space="preserve">Crear centros gestores y posiciones presupuestarias</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPSA, OPSK, OPSJ</t>
+          <t xml:space="preserve">FMSA (centros gestores), FMCIA (posiciones)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TCJ41 / PRPS</t>
+          <t xml:space="preserve">FMFCTR / FMCI</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Proyectos / PMO</t>
+          <t xml:space="preserve">Presupuesto / Planeación Financiera</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor PS</t>
+          <t xml:space="preserve">Consultor FM</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3124,24 +3140,24 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proyectos con estructura PEP para planear, ejecutar y controlar costes.</t>
+          <t xml:space="preserve">Ej.: centros gestores por gerencia y posiciones por naturaleza del gasto.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">43</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9. Proyectos (PS)</t>
+          <t xml:space="preserve">8. Control presupuestal (FM)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Los proyectos de inversión deben capitalizarse en activos fijos?</t>
+          <t xml:space="preserve">¿Se necesitará control de imputación para ejecuciones de proyectos (CAPEX / OPEX)?</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3151,27 +3167,27 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configurar perfil de inversión y liquidación a activo en curso; Proyectos solo de gasto (liquidan a centros de coste)</t>
+          <t xml:space="preserve">Configurar derivación de imputaciones presupuestarias y control de disponibilidad</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OITA, OKO7</t>
+          <t xml:space="preserve">FMDERIVE, OF39</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAPRF / TKB1, TKB1</t>
+          <t xml:space="preserve">Estrategia de derivación FM / FMAVC</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Proyectos / PMO</t>
+          <t xml:space="preserve">Presupuesto / Planeación Financiera</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor PS</t>
+          <t xml:space="preserve">Consultor FM</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3181,14 +3197,14 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liquidación del proyecto a activo en curso (AeC) y luego al activo final.</t>
+          <t xml:space="preserve">Que el gasto de proyectos consuma presupuesto según su clasificación CAPEX u OPEX.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10. Tesorería (TR/TRM)</t>
+          <t xml:space="preserve">9. Proyectos (PS)</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3245,47 +3261,47 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43</t>
+          <t xml:space="preserve">44</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10. Tesorería (TR/TRM)</t>
+          <t xml:space="preserve">9. Proyectos (PS)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Con qué bancos operará la sociedad (cuentas bancarias propias)?</t>
+          <t xml:space="preserve">¿La sociedad ejecutará proyectos (inversión u obras) con el módulo PS?</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seleccionar valor(es) del catálogo «Bancos (ejemplo, editable)».</t>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definir bancos propios y cuentas bancarias</t>
+          <t xml:space="preserve">Definir perfil de proyecto y máscara de codificación PEP</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FI12, App Fiori Gestionar cuentas de banco (BAM)</t>
+          <t xml:space="preserve">OPSA, OPSK, OPSJ</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T012 / T012K / FCLM_BAM_ACLINK2</t>
+          <t xml:space="preserve">TCJ41 / PRPS</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesorería</t>
+          <t xml:space="preserve">Gerencia de Proyectos / PMO</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor TR / TRM</t>
+          <t xml:space="preserve">Consultor PS</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3295,121 +3311,121 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agregue cada banco desde el catálogo (puede cargar el listado de bancos de su país en Administración &gt; Catálogos).</t>
+          <t xml:space="preserve">Proyectos con estructura PEP para planear, ejecutar y controlar costes.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">9. Proyectos (PS)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Los proyectos de inversión deben capitalizarse en activos fijos?</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configurar perfil de inversión y liquidación a activo en curso; Proyectos solo de gasto (liquidan a centros de coste)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OITA, OKO7</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAPRF / TKB1, TKB1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerencia de Proyectos / PMO</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor PS</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liquidación del proyecto a activo en curso (AeC) y luego al activo final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10. Tesorería (TR/TRM)</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Se procesarán extractos bancarios electrónicos (conciliación automática)?</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Configurar extracto bancario electrónico; Conciliación bancaria manual</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OT83 (config.), FF_5 (carga), FF67</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T028B / T028G</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tesorería</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor TR / TRM</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Carga de extractos MT940/CAMT.053 con compensación automática de partidas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10. Tesorería (TR/TRM)</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Se requiere posición de caja y previsión de liquidez (Cash Management)?</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Activar Cash Management y fuentes de datos</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Apps Fiori Cash Flow Analyzer, FQM_ACTIVATE</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FQM_FLOW</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tesorería</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor TR / TRM</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visibilidad diaria de saldos bancarios y proyección de flujos.</t>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -3426,121 +3442,121 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿La sociedad manejará instrumentos financieros (inversiones, deuda, derivados) con TRM?</t>
+          <t xml:space="preserve">¿Con qué bancos operará la sociedad (cuentas bancarias propias)?</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Seleccionar valor(es) del catálogo «Bancos (ejemplo, editable)».</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definir bancos propios y cuentas bancarias</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FI12, App Fiori Gestionar cuentas de banco (BAM)</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T012 / T012K / FCLM_BAM_ACLINK2</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesorería</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor TR / TRM</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agregue cada banco desde el catálogo (puede cargar el listado de bancos de su país en Administración &gt; Catálogos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Tesorería (TR/TRM)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se procesarán extractos bancarios electrónicos (conciliación automática)?</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Configurar Treasury and Risk Management (Transaction Manager)</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SPRO (TRM), FTR_CREATE</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tipos de producto y de operación (VTBFHA…)</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configurar extracto bancario electrónico; Conciliación bancaria manual</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OT83 (config.), FF_5 (carga), FF67</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T028B / T028G</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tesorería</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Consultor TR / TRM</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CDT/depósitos, créditos, bonos, forwards de divisas, coberturas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11. Ventas y facturación (SD)</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carga de extractos MT940/CAMT.053 con compensación automática de partidas.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11. Ventas y facturación (SD)</t>
+          <t xml:space="preserve">10. Tesorería (TR/TRM)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿La sociedad facturará ventas (gestión de facturación SD)?</t>
+          <t xml:space="preserve">¿Se requiere posición de caja y previsión de liquidez (Cash Management)?</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3550,27 +3566,27 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crear/asignar estructura organizativa de ventas</t>
+          <t xml:space="preserve">Activar Cash Management y fuentes de datos</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OVX5, OVX3 (asignación)</t>
+          <t xml:space="preserve">Apps Fiori Cash Flow Analyzer, FQM_ACTIVATE</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TVKO / TVKO-BUKRS</t>
+          <t xml:space="preserve">FQM_FLOW</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial / Facturación</t>
+          <t xml:space="preserve">Tesorería</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor SD</t>
+          <t xml:space="preserve">Consultor TR / TRM</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -3580,24 +3596,24 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ventas de bienes o servicios con pedidos, entregas y facturas.</t>
+          <t xml:space="preserve">Visibilidad diaria de saldos bancarios y proyección de flujos.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">49</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11. Ventas y facturación (SD)</t>
+          <t xml:space="preserve">10. Tesorería (TR/TRM)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿La facturación debe emitirse electrónicamente ante la autoridad fiscal?</t>
+          <t xml:space="preserve">¿La sociedad manejará instrumentos financieros (inversiones, deuda, derivados) con TRM?</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3607,27 +3623,27 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configurar facturación electrónica (eDocument / Document Compliance); Facturación en papel/PDF sin reporte electrónico</t>
+          <t xml:space="preserve">Configurar Treasury and Risk Management (Transaction Manager)</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDOC_COCKPIT</t>
+          <t xml:space="preserve">SPRO (TRM), FTR_CREATE</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDOC* (marco eDocument)</t>
+          <t xml:space="preserve">Tipos de producto y de operación (VTBFHA…)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial / Facturación</t>
+          <t xml:space="preserve">Tesorería</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor SD</t>
+          <t xml:space="preserve">Consultor TR / TRM</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -3637,14 +3653,14 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facturación electrónica legal (DIAN, SAT, SUNAT, SII, etc.).</t>
+          <t xml:space="preserve">CDT/depósitos, créditos, bonos, forwards de divisas, coberturas.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12. Compras e inventarios (MM)</t>
+          <t xml:space="preserve">11. Ventas y facturación (SD)</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3701,17 +3717,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12. Compras e inventarios (MM)</t>
+          <t xml:space="preserve">11. Ventas y facturación (SD)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿La sociedad comprará materiales/servicios y manejará inventarios (MM)?</t>
+          <t xml:space="preserve">¿La sociedad facturará ventas (gestión de facturación SD)?</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3721,27 +3737,27 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crear centros/almacenes y asignarlos a la sociedad</t>
+          <t xml:space="preserve">Crear/asignar estructura organizativa de ventas</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX10, OX18 (asignación), OX09 (almacenes)</t>
+          <t xml:space="preserve">OVX5, OVX3 (asignación)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T001W / T001K / T320</t>
+          <t xml:space="preserve">TVKO / TVKO-BUKRS</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras / Logística</t>
+          <t xml:space="preserve">Comercial / Facturación</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor MM</t>
+          <t xml:space="preserve">Consultor SD</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3751,225 +3767,225 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras con pedido, entradas de mercancía y verificación de facturas.</t>
+          <t xml:space="preserve">Ventas de bienes o servicios con pedidos, entregas y facturas.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">51</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11. Ventas y facturación (SD)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿La facturación debe emitirse electrónicamente ante la autoridad fiscal?</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configurar facturación electrónica (eDocument / Document Compliance); Facturación en papel/PDF sin reporte electrónico</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDOC_COCKPIT</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EDOC* (marco eDocument)</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial / Facturación</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor SD</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Facturación electrónica legal (DIAN, SAT, SUNAT, SII, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">12. Compras e inventarios (MM)</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Cómo se valorarán los inventarios?</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Elegir una opción: Precio estándar (S) | Precio medio variable (V)</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Definir control de precio estándar y cálculo de costes; Definir control de precio media móvil</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OMW0, CK11N, CK24</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MBEW-VPRSV = S, MBEW-VPRSV = V</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12. Compras e inventarios (MM)</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿La sociedad comprará materiales/servicios y manejará inventarios (MM)?</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crear centros/almacenes y asignarlos a la sociedad</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OX10, OX18 (asignación), OX09 (almacenes)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T001W / T001K / T320</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Compras / Logística</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Consultor MM</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control de precio del material: estándar o media móvil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12. Compras e inventarios (MM)</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿La verificación de facturas de compras tendrá tolerancias y bloqueos de pago?</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Definir tolerancias de verificación de facturas; Verificación sin tolerancias específicas (valores estándar)</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OMR6</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">T169G</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Compras / Logística</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Consultor MM</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Diferencias permitidas entre pedido, entrada de mercancía y factura (3-way match).</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13. Mantenimiento (PM)</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras con pedido, entradas de mercancía y verificación de facturas.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13. Mantenimiento (PM)</t>
+          <t xml:space="preserve">12. Compras e inventarios (MM)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿La sociedad gestionará mantenimiento de equipos y activos (PM)?</t>
+          <t xml:space="preserve">¿Cómo se valorarán los inventarios?</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+          <t xml:space="preserve">Elegir una opción: Precio estándar (S) | Precio medio variable (V)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definir centros de emplazamiento y de planificación de mantenimiento</t>
+          <t xml:space="preserve">Definir control de precio estándar y cálculo de costes; Definir control de precio media móvil</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPRO</t>
+          <t xml:space="preserve">OMW0, CK11N, CK24</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T001W-IWERK</t>
+          <t xml:space="preserve">MBEW-VPRSV = S, MBEW-VPRSV = V</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento</t>
+          <t xml:space="preserve">Compras / Logística</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor PM</t>
+          <t xml:space="preserve">Consultor MM</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -3979,24 +3995,24 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento correctivo/preventivo de maquinaria, vehículos, instalaciones.</t>
+          <t xml:space="preserve">Control de precio del material: estándar o media móvil.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13. Mantenimiento (PM)</t>
+          <t xml:space="preserve">12. Compras e inventarios (MM)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">¿Se usarán órdenes de mantenimiento con costes imputados a CO?</t>
+          <t xml:space="preserve">¿La verificación de facturas de compras tendrá tolerancias y bloqueos de pago?</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4006,27 +4022,27 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Configurar tipos de orden PM e integración con CO; Mantenimiento solo con avisos (sin costes por orden)</t>
+          <t xml:space="preserve">Definir tolerancias de verificación de facturas; Verificación sin tolerancias específicas (valores estándar)</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OIOA, OKO7</t>
+          <t xml:space="preserve">OMR6</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">T003O</t>
+          <t xml:space="preserve">T169G</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento</t>
+          <t xml:space="preserve">Compras / Logística</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor PM</t>
+          <t xml:space="preserve">Consultor MM</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -4036,14 +4052,14 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Órdenes correctivas/preventivas que recogen costes de repuestos y mano de obra.</t>
+          <t xml:space="preserve">Diferencias permitidas entre pedido, entrada de mercancía y factura (3-way match).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14. Documentos contables</t>
+          <t xml:space="preserve">13. Mantenimiento (PM)</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4100,55 +4116,226 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">13. Mantenimiento (PM)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿La sociedad gestionará mantenimiento de equipos y activos (PM)?</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definir centros de emplazamiento y de planificación de mantenimiento</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPRO</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T001W-IWERK</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor PM</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo/preventivo de maquinaria, vehículos, instalaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13. Mantenimiento (PM)</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se usarán órdenes de mantenimiento con costes imputados a CO?</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decidir Sí / No y, si aplica, su alcance.</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Configurar tipos de orden PM e integración con CO; Mantenimiento solo con avisos (sin costes por orden)</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OIOA, OKO7</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">T003O</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor PM</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Órdenes correctivas/preventivas que recogen costes de repuestos y mano de obra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">14. Documentos contables</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14. Documentos contables</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">¿Cómo se crearán los rangos de números de documento contable?</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Elegir una opción: Copiar rangos desde una sociedad de referencia | Crear rangos manualmente</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Copiar rangos de números de documento; Crear rangos de números de documento</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OBH1, FBN1</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NRIV (objeto RF_BELEG)</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Contabilidad General</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Consultor FI</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cada clase de documento (KR, DR, SA…) necesita un rango de numeración por sociedad.</t>
         </is>
@@ -4164,13 +4351,13 @@
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="38" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4263,7 +4450,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Considerar número de cuenta alternativo (plan local).</t>
+          <t xml:space="preserve">Ver hoja «Detalle Datos Maestros» para el nivel de campo.</t>
         </is>
       </c>
     </row>
@@ -4275,32 +4462,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner – Proveedores</t>
+          <t xml:space="preserve">CECO – Centros de coste</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Datos generales, rol FLVN00/FLVN01, datos de sociedad y compras</t>
+          <t xml:space="preserve">Jerarquía estándar, centros con responsable y CeBe, grupos alternativos</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BP / MDG-S</t>
+          <t xml:space="preserve">OKEON / KS01 / KSH1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cuentas por Pagar / Compras</t>
+          <t xml:space="preserve">Costos / Planeación</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipo de Datos Maestros</t>
+          <t xml:space="preserve">Consultor CO</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cuentas por Pagar</t>
+          <t xml:space="preserve">Gerencia de Planeación</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -4310,7 +4497,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CVI activo: integra proveedor FI y MM.</t>
+          <t xml:space="preserve">Ver detalle: codificación, clases de centro, bloqueos, ciclos.</t>
         </is>
       </c>
     </row>
@@ -4322,32 +4509,32 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business Partner – Clientes</t>
+          <t xml:space="preserve">CEBE – Centros de beneficio</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Datos generales, rol FLCU00/FLCU01, datos de sociedad y ventas</t>
+          <t xml:space="preserve">Jerarquía estándar, CEBEs por línea de negocio, dummy y derivación</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BP / MDG-C</t>
+          <t xml:space="preserve">KCH1 / KE51 / FAGL3KEH</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartera / Comercial</t>
+          <t xml:space="preserve">Costos / Planeación</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipo de Datos Maestros</t>
+          <t xml:space="preserve">Consultor CO/FI</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crédito y Cartera</t>
+          <t xml:space="preserve">Gerencia Financiera</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -4357,7 +4544,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asignar procedimiento de reclamación y datos de crédito.</t>
+          <t xml:space="preserve">Ver detalle: segmentos asignados y reglas de derivación.</t>
         </is>
       </c>
     </row>
@@ -4369,32 +4556,32 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maestro de Bancos propios y Casa de bancos</t>
+          <t xml:space="preserve">Segmentos (NIIF 8)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claves de banco, cuentas bancarias (BAM)</t>
+          <t xml:space="preserve">Segmentos reportables asignados a los CEBEs</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FI01 / FI12 / App Gestionar cuentas de banco</t>
+          <t xml:space="preserve">SPRO (Definir segmento)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesorería</t>
+          <t xml:space="preserve">Contabilidad / Consolidación</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor FI / Tesorería</t>
+          <t xml:space="preserve">Consultor FI-GL</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Tesorería</t>
+          <t xml:space="preserve">Gerencia de Contabilidad</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -4404,7 +4591,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definir cuentas de mayor por banco y transitorias.</t>
+          <t xml:space="preserve">Requiere desglose de documentos para balances por segmento.</t>
         </is>
       </c>
     </row>
@@ -4416,22 +4603,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maestro de Materiales</t>
+          <t xml:space="preserve">Business Partner – Proveedores</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vistas básicas, contabilidad, compras, ventas; tipo y grupo de materiales</t>
+          <t xml:space="preserve">Agrupaciones, roles 000000/FLVN00/FLVN01, datos fiscales, bancarios y de retención</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MM01 / MDG-M</t>
+          <t xml:space="preserve">BP / MDG-S</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras / Logística</t>
+          <t xml:space="preserve">Cuentas por Pagar / Compras</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4441,7 +4628,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logística / Costos</t>
+          <t xml:space="preserve">Cuentas por Pagar</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -4451,7 +4638,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solo si la sociedad usa MM. Definir control de precio (S/V).</t>
+          <t xml:space="preserve">Ver detalle por rol. CVI activo obligatorio en S/4HANA.</t>
         </is>
       </c>
     </row>
@@ -4463,32 +4650,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maestro de Activos Fijos</t>
+          <t xml:space="preserve">Business Partner – Clientes</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Altas por clase de activo, datos de valoración y amortización</t>
+          <t xml:space="preserve">Agrupaciones, roles 000000/FLCU00/FLCU01, crédito y reclamación</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AS01 / AS91 (saldos iniciales)</t>
+          <t xml:space="preserve">BP / MDG-C</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contabilidad de Activos Fijos</t>
+          <t xml:space="preserve">Cartera / Comercial</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor FI-AA</t>
+          <t xml:space="preserve">Equipo de Datos Maestros</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Contabilidad</t>
+          <t xml:space="preserve">Crédito y Cartera</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4498,7 +4685,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AS91 para migración de saldos de activos.</t>
+          <t xml:space="preserve">Ver detalle por rol: cuenta asociada, dunning, datos de ventas.</t>
         </is>
       </c>
     </row>
@@ -4510,32 +4697,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centros de coste y Jerarquía estándar</t>
+          <t xml:space="preserve">Maestro de Bancos y cuentas (BAM)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estructura organizativa de costos y responsables</t>
+          <t xml:space="preserve">Claves de banco, bancos propios, cuentas con firmantes y cuentas GL vinculadas</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">KS01 / OKEON</t>
+          <t xml:space="preserve">FI01 / FI12 / App BAM</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costos / Planeación</t>
+          <t xml:space="preserve">Tesorería</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor CO</t>
+          <t xml:space="preserve">Consultor TR / Tesorería</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Planeación</t>
+          <t xml:space="preserve">Gerencia de Tesorería</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -4545,7 +4732,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicitar listado con responsables por centro.</t>
+          <t xml:space="preserve">Incluye transitorias por vía de pago para conciliación.</t>
         </is>
       </c>
     </row>
@@ -4557,32 +4744,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clases de coste (primarias/secundarias)</t>
+          <t xml:space="preserve">Maestro de Materiales</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">En S/4HANA son cuentas de mayor tipo coste</t>
+          <t xml:space="preserve">Vistas básicas, contabilidad (control de precio), compras y ventas</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FS00 (tipo de cuenta)</t>
+          <t xml:space="preserve">MM01 / MDG-M</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costos / Contabilidad</t>
+          <t xml:space="preserve">Compras / Logística</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor CO / FI</t>
+          <t xml:space="preserve">Equipo de Datos Maestros</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Contabilidad</t>
+          <t xml:space="preserve">Logística / Costos</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -4592,7 +4779,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Integradas al ledger universal.</t>
+          <t xml:space="preserve">Solo si la sociedad usa MM.</t>
         </is>
       </c>
     </row>
@@ -4604,32 +4791,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centros gestores y Posiciones presupuestarias</t>
+          <t xml:space="preserve">Maestro de Activos Fijos</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Datos maestros de Funds Management</t>
+          <t xml:space="preserve">Altas por clase, valoración y amortización; saldos iniciales con AS91</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FMSA / FMCIA</t>
+          <t xml:space="preserve">AS01 / AS91</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presupuesto</t>
+          <t xml:space="preserve">Contab. Activos Fijos</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor FM</t>
+          <t xml:space="preserve">Consultor FI-AA</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia Financiera</t>
+          <t xml:space="preserve">Gerencia de Contabilidad</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -4639,7 +4826,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solo si hay control presupuestal (FM).</t>
+          <t xml:space="preserve">Ver detalle: intervalos, determinación de cuentas, vidas útiles.</t>
         </is>
       </c>
     </row>
@@ -4651,32 +4838,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maestro de Proyectos / PEP</t>
+          <t xml:space="preserve">Centros gestores y Posiciones presupuestarias</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Definiciones de proyecto y elementos PEP</t>
+          <t xml:space="preserve">Datos maestros de FM con jerarquías</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CJ20N / CJ01</t>
+          <t xml:space="preserve">FMSA / FMCIA</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Proyectos</t>
+          <t xml:space="preserve">Presupuesto</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor PS</t>
+          <t xml:space="preserve">Consultor FM</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PMO</t>
+          <t xml:space="preserve">Gerencia Financiera</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -4686,7 +4873,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solo si la sociedad usa PS.</t>
+          <t xml:space="preserve">Solo si hay control presupuestal.</t>
         </is>
       </c>
     </row>
@@ -4698,32 +4885,32 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipos de cambio (cotizaciones)</t>
+          <t xml:space="preserve">Maestro de Proyectos / PEP</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tasas por tipo de cotización y moneda</t>
+          <t xml:space="preserve">Definiciones de proyecto y elementos PEP</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OB08 / TCURR</t>
+          <t xml:space="preserve">CJ20N / CJ01</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesorería / Contabilidad</t>
+          <t xml:space="preserve">Gerencia de Proyectos</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor FI / Tesorería</t>
+          <t xml:space="preserve">Consultor PS</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Tesorería</t>
+          <t xml:space="preserve">PMO</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -4733,7 +4920,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantener para todas las monedas paralelas/operativas.</t>
+          <t xml:space="preserve">Solo si la sociedad usa PS.</t>
         </is>
       </c>
     </row>
@@ -4745,32 +4932,32 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condiciones de pago</t>
+          <t xml:space="preserve">Tipos de cambio</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Términos de pago de clientes y proveedores</t>
+          <t xml:space="preserve">Cotizaciones por tipo y moneda con responsable de actualización</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBB8</t>
+          <t xml:space="preserve">OB08 / TCURR</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesorería / Cartera</t>
+          <t xml:space="preserve">Tesorería / Contabilidad</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor FI</t>
+          <t xml:space="preserve">Consultor FI / Tesorería</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia Financiera</t>
+          <t xml:space="preserve">Gerencia de Tesorería</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -4780,7 +4967,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compartidas entre AP y AR.</t>
+          <t xml:space="preserve">Para todas las monedas paralelas y operativas.</t>
         </is>
       </c>
     </row>
@@ -4792,32 +4979,32 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indicadores e impuestos / Retenciones</t>
+          <t xml:space="preserve">Condiciones de pago</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Códigos de IVA y de retención y sus cuentas</t>
+          <t xml:space="preserve">Términos de pago de clientes y proveedores</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTXP / tablas T059</t>
+          <t xml:space="preserve">OBB8</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Área Tributaria</t>
+          <t xml:space="preserve">Tesorería / Cartera</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultor FI (Tax)</t>
+          <t xml:space="preserve">Consultor FI</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Impuestos</t>
+          <t xml:space="preserve">Gerencia Financiera</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -4827,7 +5014,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Levantar matriz tributaria del país.</t>
+          <t xml:space="preserve">Compartidas entre AP y AR.</t>
         </is>
       </c>
     </row>
@@ -4839,42 +5026,89 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empleados / Usuarios y autorizaciones</t>
+          <t xml:space="preserve">Indicadores de impuestos / Retenciones</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roles y autorizaciones por área</t>
+          <t xml:space="preserve">Códigos de IVA y retención con cuentas asignadas</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SU01 / PFCG</t>
+          <t xml:space="preserve">FTXP / OB40 / T059</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguridad / RRHH</t>
+          <t xml:space="preserve">Área Tributaria</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Consultor FI (Tax)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerencia de Impuestos</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Levantar matriz tributaria del país.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuarios y autorizaciones</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuarios, roles por área y matriz SoD; grupos de tolerancia asignados</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SU01 / PFCG / OB57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seguridad / Dueños de proceso</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Equipo de Seguridad (BASIS/GRC)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Dueños de proceso</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Definir matriz de segregación de funciones (SoD).</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin grupo de tolerancia el usuario no puede contabilizar.</t>
         </is>
       </c>
     </row>
@@ -4886,314 +5120,3456 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Área / Rol</t>
+          <t xml:space="preserve">#</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipo</t>
+          <t xml:space="preserve">Objeto</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Responsabilidad principal en la creación de la sociedad</t>
+          <t xml:space="preserve">Definición de detalle requerida</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Información que debe entregar el negocio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transacción / App</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área que DEFINE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área que CREA/CARGA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estado</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CECO – Centros de coste</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CECO – Centros de coste</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Máscara y rango de codificación de CECOs</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estándar de codificación (longitud, prefijo por sociedad/área, ej. C001-1010)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definición de proyecto</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debe ser coherente entre todas las sociedades del grupo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CECO – Centros de coste</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jerarquía estándar (nodos por gerencia / vicepresidencia / área)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Organigrama vigente con niveles de agregación para reportes</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OKEON</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La jerarquía estándar es obligatoria antes de crear el primer CECO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CECO – Centros de coste</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listado de CECOs con datos completos por centro</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por cada CECO: código, denominación, responsable (nombre/usuario), clase de centro (producción, administración, ventas, servicios), área funcional, moneda, CeBe asignado, fecha de validez</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KS01 / KS02 (masivo: app Fiori o LTMC)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO / Datos Maestros</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin CeBe asignado en el maestro, la derivación CECO→CeBe falla al contabilizar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CECO – Centros de coste</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grupos alternativos de CECOs para reportes y autorizaciones</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agrupaciones por gerencia, proyecto o naturaleza para reporting y roles</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KSH1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Opcional pero recomendado para reportes y restricción de autorizaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CECO – Centros de coste</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bloqueos y restricciones por CECO</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué CECOs aceptan imputaciones primarias, secundarias, ingresos o compromisos</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KS02 (pestaña Control)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evita imputaciones erradas (ej. ingresos en centros administrativos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CECO – Centros de coste</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ciclos de distribución / subreparto (si aplica)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reglas de reparto de costes indirectos: emisores, receptores, criterios (%/estadísticos)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KSV1 / KSU1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definir si el modelo de costeo lo requiere desde el arranque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEBE – Centros de beneficio</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEBE – Centros de beneficio</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Máscara y rango de codificación de CEBEs</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estándar de codificación por línea/unidad de negocio o región</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definición de proyecto</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO/FI</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coherente con el modelo de rentabilidad del grupo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEBE – Centros de beneficio</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jerarquía estándar de CEBEs</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estructura de líneas/unidades de negocio con niveles de agregación</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KCH1 / KCH5N</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO/FI</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asignada en la sociedad CO (0KE5).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEBE – Centros de beneficio</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listado de CEBEs con datos completos</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por cada CeBe: código, denominación, responsable, segmento asignado, sociedad(es) válida(s), fecha de validez</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KE51 / KE52</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO/FI</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El segmento se deriva del CeBe: si falta, el desglose por segmento falla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEBE – Centros de beneficio</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CeBe dummy / por defecto</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CeBe a usar cuando ninguna regla deriva un valor (ej. código de la sociedad)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KE51 + FAGL3KEH</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO/FI</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obligatorio si el desglose exige CeBe en toda partida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEBE – Centros de beneficio</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reglas de derivación de CeBe</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matriz: CECO→CeBe (maestro KS02), material/centro→CeBe (maestro MM), cuenta→CeBe por defecto (FAGL3KEH), orden CO→CeBe</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KS02 / MM02 / FAGL3KEH</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO/FI</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probar con asientos de cada proceso (compras, ventas, nómina, manual).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – General</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – General</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agrupaciones de BP y rangos de números</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agrupaciones (proveedor nacional, exterior, empleado, cliente nacional, exterior, ICO) y si la numeración es interna o externa</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUCF + customizing BP</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos Maestros / Finanzas</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI / MDG</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La agrupación determina el rango y los campos obligatorios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – General</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sincronización BP ↔ proveedor/cliente (CVI)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verificar que la integración CVI esté activa y los rangos enlazados</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customizing CVI</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TI / Datos Maestros</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor técnico</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En S/4HANA es obligatorio operar vía BP, no FK01/FD01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – Proveedores</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – Proveedores</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos generales por proveedor</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Razón social, identificación fiscal (NIT/RFC/RUC con dígito de verificación), tipo de identificación, dirección completa, contacto, idioma</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (rol 000000)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas por Pagar / Compras</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos Maestros</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La identificación fiscal alimenta reportes legales (medios magnéticos, DIOT, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – Proveedores</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rol FI (FLVN00): datos de sociedad</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por proveedor y sociedad: cuenta asociada, condiciones de pago, vías de pago permitidas, banco propio por defecto, datos bancarios del proveedor (banco, cuenta, IBAN), indicadores de retención aplicables, bloqueos</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (rol FLVN00)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas por Pagar</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos Maestros</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin cuenta asociada NO se puede contabilizar ninguna factura al proveedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – Proveedores</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rol Compras (FLVN01): datos de organización de compras</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Org. de compras, moneda de pedido, condiciones de pago de compras, incoterms, verificación de factura basada en EM</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (rol FLVN01)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos Maestros</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solo si la sociedad usa MM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – Clientes</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – Clientes</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos generales por cliente</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Razón social, identificación fiscal, dirección fiscal y de entrega, contactos, clasificación fiscal</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (rol 000000)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartera / Comercial</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos Maestros</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La clasificación fiscal determina el IVA en ventas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – Clientes</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rol FI (FLCU00): datos de sociedad</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuenta asociada, condiciones de pago, procedimiento de reclamación (dunning), persona de cobranza, bloqueos</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (rol FLCU00)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartera</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos Maestros</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin cuenta asociada NO se puede facturar ni contabilizar al cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – Clientes</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rol Ventas (FLCU01): datos de área de ventas</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Org. de ventas/canal/sector, zona de ventas, grupo de precios, condiciones de expedición, clasificación fiscal por categoría</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (rol FLCU01)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos Maestros</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solo si la sociedad usa SD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP – Clientes</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos de crédito (FSCM)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Segmento de crédito, límite de crédito, clase de riesgo, reglas de verificación</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP (rol UKM000) / UKM_MY_DCDS</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crédito y Cobranza</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AR</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solo si se activó gestión de crédito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas de mayor</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas de mayor</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Segmento de sociedad por cada cuenta del plan</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por cuenta: moneda, gestión de partidas abiertas/visualización individual, grupo de status de campo, clave de clasificación (sort key), relevancia de flujo de caja, indicador de impuestos permitido</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FS00 / OB_GLACC11 (masivo)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-GL</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Una cuenta sin segmento de sociedad bloquea cualquier asiento que la use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas de mayor</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas asociadas (reconciliation accounts)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas de deudores, acreedores y activos fijos por tipo (nacional, exterior, ICO, anticipos CME)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FS00 (tipo cuenta asociada) + OBYR/OBXR</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definirlas ANTES de crear BPs: el BP exige la cuenta asociada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas de mayor</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas técnicas y de operación obligatorias</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Retención de beneficios (OB53), diferencias de cambio realizadas/no realizadas (OBA1), redondeo, compensación EM/RF (WRX/GR-IR), diferencias menores, cuentas puente de migración, bancos transitorias</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OB53 / OBA1 / OBYC / FS00</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin OB53 no se puede cerrar el primer ejercicio; sin OBA1 no compensan partidas en moneda extranjera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas de mayor</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clasificación de cuentas para el desglose de documentos</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categoría de posición por rango de cuentas (deudores, acreedores, impuestos, bancos, materiales, PyG)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPRO (desglose) </t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-GL</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solo si hay document splitting: una cuenta sin clasificar bloquea el asiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activos fijos</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activos fijos</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intervalos de numeración por clase de activo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rango de números interno por cada clase (terrenos, edificios, maquinaria, vehículos, cómputo, AeC...)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AS08</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contab. Activos Fijos</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AA</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Los rangos no se transportan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activos fijos</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Determinación de cuentas por clase</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas de coste de adquisición, amortización acumulada, gasto de amortización, bajas, utilidad/pérdida en venta</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AO90</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contab. Activos Fijos</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AA</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Una clase sin determinación de cuentas impide capitalizar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activos fijos</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matriz de vidas útiles y claves de amortización</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por clase y por área de valoración (local/NIIF/fiscal): método, vida útil, valor residual, inicio de amortización</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AFAMA + maestro AS01</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contab. Activos Fijos</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AA</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validar con políticas contables y normativa fiscal del país.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bancos</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bancos</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claves de banco del país</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Catálogo de bancos con código ACH/ABA/SWIFT según el país</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FI01 (o carga del directorio bancario)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesorería</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI / Basis</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Puede cargarse el directorio bancario oficial del país.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bancos</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bancos propios y cuentas bancarias (BAM)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por cuenta: banco, número de cuenta/IBAN, moneda, descripción, firmantes/aprobadores, cuenta de mayor principal</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FI12 / App Gestionar cuentas de banco</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesorería</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor TR</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En S/4HANA las cuentas son datos maestros con flujo de aprobación (BAM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bancos</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas contables transitorias por vía de pago</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estructura de cuentas: principal + transitorias (cheques emitidos, transferencias salientes, entradas) por banco</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FS00 + FBZP</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesorería / Contabilidad</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor TR/FI</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Necesarias para conciliación automática del extracto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación contable</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación contable</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grupos de tolerancia de empleados y asignación de usuarios</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importe máximo por documento, por partida y % de descuento permitido por grupo de usuarios; asignar usuarios a grupos</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBA4 + OB57</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SIN GRUPO DE TOLERANCIA NADIE PUEDE CONTABILIZAR. Definir grupo en blanco o por usuario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación contable</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tolerancias de compensación para BPs</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diferencias permitidas al compensar partidas de clientes/proveedores</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBA3</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requerida para compensaciones (F-32/F-44) y pagos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación contable</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clases de documento y claves de contabilización</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verificar clases estándar (SA, KR, KZ, DR, DZ, AB...) y claves (40/50, 31/21, 01/11...) o definir propias</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBA7 / OB41</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cada clase debe tener rango de números asignado en la sociedad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación contable</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indicadores de impuestos por defecto para cuentas sin impuesto</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Indicadores de entrada/salida 0% para operaciones no gravadas</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBCL</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área Tributaria</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin esto fallan asientos en cuentas marcadas como relevantes de impuesto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación contable</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipos de cambio y cotizaciones iniciales</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipos de cotización (M, compra, venta, cierre) y tasas vigentes para todas las monedas operativas</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OB08 / TCURR</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesorería</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definir responsable y frecuencia de actualización (manual o interfaz).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operación contable</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apertura de períodos contables y de CO</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Período actual abierto para todas las clases de cuenta (+, A, D, K, M, S) y períodos CO</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OB52 + OKP1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI/CO</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Definir gobierno mensual de apertura/cierre.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verificación (criterio de aceptación)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transacción / Evidencia</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Responsable</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bloqueante</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estado</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PMO / Líder de Finanzas</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Sociedad creada con datos completos (razón social, dirección, país, moneda, idioma)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coordina el levantamiento, valida alcance y aprueba definiciones generales.</t>
+          <t xml:space="preserve">OX02 — T001 completa</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contabilidad General</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Asignaciones organizativas: plan de cuentas, variante ejercicio, variante períodos, variante status campo, sociedad CO</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define plan de cuentas, estructura de balance, períodos, validaciones y cierre.</t>
+          <t xml:space="preserve">OB62 / OB37 / OBBP / OBC5 / OX19</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Área Tributaria / Impuestos</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Ledgers y monedas (10/30) verificados ANTES de cualquier asiento</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define matriz de IVA, retenciones, lugares comerciales y facturación electrónica.</t>
+          <t xml:space="preserve">FINSC_LEDGER — revisar parametrización de moneda</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-GL</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cuentas por Pagar</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Desglose de documentos decidido y, si aplica, configurado y probado (CeBe/segmento, saldo cero)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define proveedores, condiciones de pago, programa de pagos y anticipos.</t>
+          <t xml:space="preserve">SPRO desglose — asiento de prueba con verificación de FAGL_SPLINFO</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-GL</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartera / Crédito y Cobranza</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Períodos contables abiertos (FI todas las clases de cuenta) y períodos CO</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define clientes, gestión de crédito, reclamaciones y anticipos.</t>
+          <t xml:space="preserve">OB52 / OKP1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contabilidad de Activos Fijos</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Rangos de números de documento creados para el ejercicio actual y siguiente</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define clases de activos, vidas útiles y plan de valoración.</t>
+          <t xml:space="preserve">FBN1 / OBH1 — verificar clases SA, KR, KZ, DR, DZ, AB</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costos / Planeación</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Clases de documento y claves de contabilización verificadas</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define centros de coste, órdenes internas y modelo de costeo.</t>
+          <t xml:space="preserve">OBA7 / OB41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Presupuesto / Planeación Financiera</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Cuentas de mayor creadas con segmento de sociedad (plan completo)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define estructura presupuestal, control de disponibilidad y CAPEX/OPEX.</t>
+          <t xml:space="preserve">FS00 / OB_GLACC11 — comparar contra plan corporativo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-GL</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gerencia de Proyectos / PMO</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Cuentas de retención de beneficios definidas</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define estructura de proyectos y capitalización de inversiones.</t>
+          <t xml:space="preserve">OB53</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-GL</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tesorería</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Cuentas de diferencia de cambio y tasas iniciales cargadas</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define bancos, medios de pago, conciliación, liquidez e instrumentos financieros.</t>
+          <t xml:space="preserve">OBA1 + OB08</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI / Tesorería</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comercial / Facturación</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Esquema de impuestos asignado al país, indicadores IVA creados con sus cuentas</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define estructura de ventas, precios y facturación.</t>
+          <t xml:space="preserve">OBBG / FTXP / OB40 — asiento de prueba con IVA</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI (Tax)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compras / Logística</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Indicadores 0% por defecto para cuentas no gravadas</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define centros, almacenes, valoración de inventarios y tolerancias.</t>
+          <t xml:space="preserve">OBCL</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI (Tax)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio</t>
+          <t xml:space="preserve">Retenciones: tipos/indicadores configurados, cuentas asignadas y sociedad activada</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Define centros de planificación y órdenes de mantenimiento.</t>
+          <t xml:space="preserve">SPRO retención ampliada + OB_WT — simulación de factura con retención</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI (Tax)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí (si aplica)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipo de Datos Maestros / MDG</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negocio/TI</t>
+          <t xml:space="preserve">Grupos de tolerancia de empleados creados y usuarios asignados</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gobierna creación y calidad de BP, materiales y cuentas centralizadas.</t>
+          <t xml:space="preserve">OBA4 + OB57</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consultores funcionales SAP (por módulo)</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Técnico</t>
+          <t xml:space="preserve">Tolerancias de compensación de BPs definidas</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecutan la parametrización en SPRO y validan con el negocio.</t>
+          <t xml:space="preserve">OBA3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipo de Migración de Datos</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Técnico</t>
+          <t xml:space="preserve">Jerarquía estándar y CECOs creados, con responsable y CeBe asignado</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecuta cargas (Migration Cockpit), concilia saldos y datos maestros.</t>
+          <t xml:space="preserve">OKEON / KS03 — muestreo de centros</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí (si usa CO)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jerarquía, CEBEs, CeBe dummy y reglas de derivación probadas</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KCH3 / KE53 / FAGL3KEH — asiento de prueba y revisión de CeBe derivado</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor CO/FI</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí (si aplica)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Segmentos definidos y asignados en maestros de CeBe</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maestro KE53 campo Segmento</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-GL</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí (si aplica)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas asociadas de deudores/acreedores/activos y CME de anticipos configuradas</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FS00 / OBYR / OBXR</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BPs proveedores y clientes creados/extendidos a la sociedad con cuenta asociada, condiciones y vía de pago</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BP — muestreo por agrupación</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Datos Maestros</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bancos propios, cuentas bancarias (BAM) y cuentas contables transitorias creadas</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FI01 / FI12 / FS00</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesorería / Consultor TR</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programa de pagos configurado y probado con pago de prueba</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FBZP + F110 en QA</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AP</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí (si aplica)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clases de activos, determinación de cuentas y claves de amortización listas</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OAOA / AO90 / AFAMA — alta de activo de prueba AS01</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI-AA</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí (si usa AA)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lugares comerciales / numeración fiscal / facturación electrónica activos</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPRO localización + EDOC_COCKPIT — documento de prueba</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultor FI (Tax) / SD</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí (si aplica)</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saldos iniciales y partidas abiertas migrados y conciliados (cuentas puente en cero)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LTMC + reporte de conciliación firmado</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipo de Migración</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí (si hay migración)</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usuarios creados con roles asignados y matriz SoD validada</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SU01 / PFCG</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seguridad (BASIS/GRC)</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prueba integral en QA: factura proveedor (FB60), factura cliente (FB70), asiento manual (FB50), pago (F110), extracto (FF_5), cierre de período de prueba</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan de pruebas firmado por el negocio</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Líder funcional + Negocio</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acta de aprobación de arranque (go-live) firmada por las áreas responsables</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documento de cut-over</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMO</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pendiente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área / Rol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Responsabilidad principal en la creación de la sociedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMO / Líder de Finanzas</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coordina el levantamiento, valida alcance y aprueba definiciones generales y el go-live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad General</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define plan de cuentas, estructura de balance, períodos, validaciones, tolerancias, desglose y cierre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área Tributaria / Impuestos</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define matriz de IVA, retenciones, lugares comerciales y facturación electrónica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuentas por Pagar</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define proveedores (datos FI), condiciones de pago, programa de pagos y anticipos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cartera / Crédito y Cobranza</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define clientes (datos FI), gestión de crédito, reclamaciones y anticipos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contabilidad de Activos Fijos</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define clases de activos, vidas útiles, plan de valoración y saldos iniciales de activos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costos / Planeación</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define CECOs, CEBEs, jerarquías, derivaciones, órdenes internas y modelo de costeo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Presupuesto / Planeación Financiera</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define estructura presupuestal, control de disponibilidad y CAPEX/OPEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gerencia de Proyectos / PMO</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define estructura de proyectos y capitalización de inversiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesorería</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define bancos, cuentas bancarias, medios de pago, conciliación, tipos de cambio, liquidez e instrumentos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comercial / Facturación</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define estructura de ventas, datos de ventas de clientes, precios y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compras / Logística</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define centros, almacenes, datos de compras de proveedores, valoración y tolerancias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define centros de planificación y órdenes de mantenimiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consolidación / Reportes corporativos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define segmentos NIIF 8, CeBe corporativos y requerimientos de reporting del grupo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipo de Datos Maestros / MDG</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Negocio/TI</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gobierna creación, extensión y calidad de BP, materiales y cuentas; ejecuta cargas masivas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consultores funcionales SAP (por módulo)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutan la parametrización en SPRO, documentan y validan con el negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Equipo de Migración de Datos</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Técnico</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecuta cargas (Migration Cockpit), concilia saldos y deja cuentas puente en cero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Seguridad / BASIS / GRC</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Técnico</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crea usuarios, roles y la matriz de segregación de funciones.</t>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crea usuarios, roles, grupos de tolerancia y la matriz de segregación de funciones.</t>
         </is>
       </c>
     </row>
